--- a/assets/constructions/examples/ctd_mhc1.xlsx
+++ b/assets/constructions/examples/ctd_mhc1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AV6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -644,11 +644,36 @@
           <t>dcsfms</t>
         </is>
       </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MM EFS200E15-4T12 CF IC908</t>
+          <t>MM ERS200B15-6T12 IC908</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -658,7 +683,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MM EFS-CF</t>
+          <t>MM ERS</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -675,22 +700,22 @@
         <v>45</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L2" t="b">
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -731,7 +756,7 @@
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
@@ -761,11 +786,22 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>PMKSH</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MM EFS100E07-4T06 CF IC908</t>
+          <t>MM EFS080E05-4T05 CF IC908</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -785,33 +821,33 @@
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>45</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L3" t="b">
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N3" t="n">
         <v>4</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>ISCAR_MM:T06</t>
+          <t>ISCAR_MM:T05</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,12 +875,12 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>9.6</v>
+        <v>7.7</v>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
@@ -878,11 +914,22 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>PMKSH</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4946160NDL16 WP15PE</t>
+          <t>4946200NDL20 WP15PE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -906,10 +953,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H4" t="n">
         <v>45</v>
@@ -918,23 +965,23 @@
         <v>0.5</v>
       </c>
       <c r="J4" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K4" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="L4" t="b">
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="N4" t="n">
         <v>4</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>DUOLOCK:DL16</t>
+          <t>DUOLOCK:DL20</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -966,21 +1013,21 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>15.5</v>
+        <v>19.3</v>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="AB4" t="n">
-        <v>15.5</v>
+        <v>19.3</v>
       </c>
       <c r="AC4" t="n">
         <v>20</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
@@ -1008,7 +1055,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>ZDL16</t>
+          <t>ZDL20</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1017,11 +1064,22 @@
         </is>
       </c>
       <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>PMKSH</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MM ERS160B12-5T10 IC908</t>
+          <t>MM EFS160B12-4T10 IC908</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1031,7 +1089,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MM ERS</t>
+          <t>MM EFS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1048,7 +1106,7 @@
         <v>45</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J5" t="n">
         <v>12</v>
@@ -1063,7 +1121,7 @@
         <v>12</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1134,11 +1192,22 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>PMKSH</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MM EFS060E05-4T05 CF IC908</t>
+          <t>MM EFS100E07-4T06 CF IC908</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1158,33 +1227,33 @@
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>45</v>
       </c>
       <c r="I6" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L6" t="b">
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N6" t="n">
         <v>4</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>ISCAR_MM:T05</t>
+          <t>ISCAR_MM:T06</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1212,12 +1281,12 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>7.7</v>
+        <v>9.6</v>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
@@ -1251,6 +1320,17 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>PMKSH</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
